--- a/Data/absences_match.xlsx
+++ b/Data/absences_match.xlsx
@@ -26,6 +26,9 @@
   </x:si>
   <x:si>
     <x:t>Raison</x:t>
+  </x:si>
+  <x:si>
+    <x:t/>
   </x:si>
 </x:sst>
 </file>
@@ -393,6 +396,20 @@
         <x:v>3</x:v>
       </x:c>
     </x:row>
+    <x:row r="2" spans="1:4">
+      <x:c r="A2" s="0">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="B2" s="0">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="C2" s="0">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="D2" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>

--- a/Data/absences_match.xlsx
+++ b/Data/absences_match.xlsx
@@ -26,9 +26,6 @@
   </x:si>
   <x:si>
     <x:t>Raison</x:t>
-  </x:si>
-  <x:si>
-    <x:t/>
   </x:si>
 </x:sst>
 </file>
@@ -396,20 +393,6 @@
         <x:v>3</x:v>
       </x:c>
     </x:row>
-    <x:row r="2" spans="1:4">
-      <x:c r="A2" s="0">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="B2" s="0">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="C2" s="0">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="D2" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-    </x:row>
   </x:sheetData>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>
